--- a/education_forms/013_child_emergency_contact_form--education_forms.xlsx
+++ b/education_forms/013_child_emergency_contact_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -916,8 +916,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'mother',_'value':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Mother', 'value': 'mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'father',_'value':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Father', 'value': 'father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'step-parent',_'value':_'stepparent'}</t>
+          <t>step-parent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Step-parent', 'value': 'stepparent'}</t>
+          <t>Step-parent</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'legal_guardian',_'value':_'guardian'}</t>
+          <t>legal_guardian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Legal Guardian', 'value': 'guardian'}</t>
+          <t>Legal Guardian</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'grandparent',_'value':_'grandparent'}</t>
+          <t>grandparent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Grandparent', 'value': 'grandparent'}</t>
+          <t>Grandparent</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'aunt_or_uncle',_'value':_'relative'}</t>
+          <t>aunt_or_uncle</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Aunt or Uncle', 'value': 'relative'}</t>
+          <t>Aunt or Uncle</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'family_friend',_'value':_'friend'}</t>
+          <t>family_friend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Family Friend', 'value': 'friend'}</t>
+          <t>Family Friend</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'neighbor',_'value':_'neighbor'}</t>
+          <t>neighbor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Neighbor', 'value': 'neighbor'}</t>
+          <t>Neighbor</t>
         </is>
       </c>
     </row>
